--- a/faculty_assignment_ODD.xlsx
+++ b/faculty_assignment_ODD.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drlak\my_projects\projects_myTimetable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nivis\my_projects\projects_myTimetable\college_Timetable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2443B050-C5C9-4022-9094-CF2706169816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2C48F9-DFA1-4639-A10A-6B6BB241D921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8070" yWindow="165" windowWidth="17925" windowHeight="10305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3270" yWindow="2295" windowWidth="20670" windowHeight="9120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CE" sheetId="1" r:id="rId1"/>
@@ -431,8 +431,9 @@
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="10.85546875" customWidth="1"/>
     <col min="4" max="4" width="10.7109375" customWidth="1"/>
-    <col min="5" max="5" width="9.5703125" customWidth="1"/>
-    <col min="6" max="7" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="7.5703125" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" customWidth="1"/>
     <col min="8" max="10" width="6.42578125" customWidth="1"/>
     <col min="11" max="11" width="8.140625" customWidth="1"/>
     <col min="12" max="12" width="6.42578125" customWidth="1"/>
@@ -480,85 +481,85 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="B3">
+        <v>1001</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="F2">
+      <c r="F3">
         <v>1</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G3" t="s">
         <v>15</v>
       </c>
-      <c r="H2">
+      <c r="H3">
         <v>1</v>
       </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
         <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>0</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -812,7 +813,7 @@
         <v>6</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="C10">
         <v>0</v>

--- a/faculty_assignment_ODD.xlsx
+++ b/faculty_assignment_ODD.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,33 +546,49 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CE,CE,CE</t>
+          <t>CE,CE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>s1,s1,s1</t>
+          <t>s1,s1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>GAMAT101,GAPHT121,UCHUT128</t>
+          <t>GAMAT101,UCHUT128</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3,3,2</t>
+          <t>3,2</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>['2', '2', '1']</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>3,1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>CE,CE</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>s1,s1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>GAMAT101,GXEST104</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1.0,1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -582,6 +598,136 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ZVL</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1002</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>GAPHT121</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>CE,CE</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>s1,s1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>GAMAT101,GXEST104</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ZADIE</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1009</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>GMEST103</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>UCHUT128</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
